--- a/pm/spine-signals-in-mmc-notes-2026-10-29.xlsx
+++ b/pm/spine-signals-in-mmc-notes-2026-10-29.xlsx
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Important limit: there are NO notes dated 2026 in MMC. The last note is May 2025; the last under Kristen's account is Aug 2024 and under Jasmine's Dec 2024; none exist under Coty's account. The SOP makes the Spine Routes app the daily driver, so program-era notes may live there or in the Friday export rather than in MMC. Everything here reflects 2023–2025 conversations, mostly a Sep–Oct 2024 "Spine BAT line" collateral sweep of podiatry and chiropractic offices. Treat it as a lead list to re-qualify, not as current intent.</t>
+          <t>CORRECTED Oct 30: notes do exist for 2026 — on the company records, not on the check-ins. This workbook was built from the activity export, which carries none; the All Companies export of Oct 30 holds 8,279 dated entries on 1,856 companies. Important limit: there are NO notes dated 2026 in MMC. The last note is May 2025; the last under Kristen's account is Aug 2024 and under Jasmine's Dec 2024; none exist under Coty's account. The SOP makes the Spine Routes app the daily driver, so program-era notes may live there or in the Friday export rather than in MMC. Everything here reflects 2023–2025 conversations, mostly a Sep–Oct 2024 "Spine BAT line" collateral sweep of podiatry and chiropractic offices. Treat it as a lead list to re-qualify, not as current intent.</t>
         </is>
       </c>
     </row>

--- a/pm/spine-signals-in-mmc-notes-2026-10-29.xlsx
+++ b/pm/spine-signals-in-mmc-notes-2026-10-29.xlsx
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CORRECTED Oct 30: notes do exist for 2026 — on the company records, not on the check-ins. This workbook was built from the activity export, which carries none; the All Companies export of Oct 30 holds 8,279 dated entries on 1,856 companies. Important limit: there are NO notes dated 2026 in MMC. The last note is May 2025; the last under Kristen's account is Aug 2024 and under Jasmine's Dec 2024; none exist under Coty's account. The SOP makes the Spine Routes app the daily driver, so program-era notes may live there or in the Friday export rather than in MMC. Everything here reflects 2023–2025 conversations, mostly a Sep–Oct 2024 "Spine BAT line" collateral sweep of podiatry and chiropractic offices. Treat it as a lead list to re-qualify, not as current intent.</t>
+          <t>CORRECTED Oct 30: notes do exist for 2026 — on the company records, not on the check-ins. This workbook was built from the activity export, which carries none; the All Companies export of Oct 30 holds 8,279 entries (3 undated) on 1,856 companies. Important limit: this workbook was built from the activity export, whose check-in notes stop in May 2025 (Kristen's last check-in note Aug 2024, Jasmine's Dec 2024, none under Coty's); the 2026 notes are on the company records instead. Program-era notes live on the company records (Oct 30 companies export), not on the check-ins. Everything here reflects 2023–2025 conversations, mostly a Sep–Oct 2024 "Spine BAT line" collateral sweep of podiatry and chiropractic offices. Treat it as a lead list to re-qualify, not as current intent.</t>
         </is>
       </c>
     </row>
